--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -723,60 +723,64 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +794,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -800,33 +804,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>1/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +842,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +852,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +909,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -937,7 +945,907 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -753,24 +753,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -945,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -983,24 +983,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1203,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1236,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1260,33 +1264,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1314,32 +1322,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1347,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1371,17 +1383,17 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1391,13 +1403,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1508,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1619,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1730,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1738,22 +1754,22 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1786,12 +1802,12 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1835,17 +1851,802 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>1/9</t>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,18 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,18 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1125,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1149,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1169,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1229,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1240,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1289,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1332,24 +1348,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1359,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1398,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1474,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1585,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -1696,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1807,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,33 +1875,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1885,32 +1933,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1918,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,37 +1994,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2033,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2083,7 +2135,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2198,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2309,7 +2361,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2414,13 +2466,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2530,12 +2586,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2646,7 +2702,919 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2052,32 +2052,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2109,33 +2113,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2163,32 +2171,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2196,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2220,32 +2232,32 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2278,32 +2290,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -2311,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2335,33 +2351,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2389,32 +2409,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2422,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2446,17 +2470,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2466,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2504,32 +2528,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2537,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2561,37 +2589,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2619,32 +2647,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2652,7 +2684,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2676,17 +2708,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2696,13 +2728,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2802,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2874,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2913,7 +2949,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2985,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3039,7 +3075,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3154,7 +3190,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3215,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3269,7 +3305,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3499,7 +3535,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3507,22 +3543,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3555,12 +3591,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3574,47 +3610,729 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
+      <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
         </is>
       </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,32 +2877,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2934,17 +2938,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2954,13 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3060,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3075,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3175,7 +3183,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3190,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3366,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3481,7 +3489,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3535,7 +3543,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3604,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3711,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3765,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3880,7 +3888,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3995,7 +4003,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4100,13 +4108,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4221,7 +4233,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4229,22 +4241,22 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4277,12 +4289,12 @@
       <c r="M33" s="2" t="inlineStr"/>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4296,43 +4308,273 @@
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W33" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X33" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y33" s="2" t="inlineStr">
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z33" s="2" t="inlineStr">
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
+      <c r="AA34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr"/>
-      <c r="AC33" s="2" t="inlineStr">
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,22 +2128,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2996,32 +2996,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3053,17 +3057,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3073,17 +3077,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3111,32 +3115,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3144,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,17 +3176,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3188,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3226,32 +3234,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3259,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,17 +3295,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3303,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3341,32 +3353,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3374,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,37 +3414,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3456,32 +3472,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -3489,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3513,29 +3533,29 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -3543,7 +3563,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3571,32 +3591,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3604,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3628,17 +3652,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3648,17 +3672,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3686,32 +3710,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -3719,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3743,32 +3771,32 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3834,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3873,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3888,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4003,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4118,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4146,32 +4174,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -4179,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4203,37 +4235,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4338,17 +4370,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4441,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4467,22 +4499,22 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4515,12 +4547,12 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4534,45 +4566,620 @@
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>11:25</t>
         </is>
       </c>
-      <c r="V35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W35" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X35" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z35" s="2" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr">
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>6/14</t>
         </is>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1176,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>85.0</t>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>85.0</t>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,18 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,7 +3433,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3444,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3553,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3801,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3944,32 +3948,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3977,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,17 +4009,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4021,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4059,32 +4067,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4092,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4116,37 +4128,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4184,24 +4196,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4211,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4260,12 +4272,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4293,32 +4305,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4326,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4350,17 +4366,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4370,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4408,32 +4424,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4441,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4465,33 +4485,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4519,32 +4543,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -4552,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4576,17 +4604,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4596,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4634,32 +4662,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4667,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4691,37 +4723,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4836,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4936,7 +4968,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4951,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5061,12 +5093,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5127,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5181,7 +5213,693 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>75.5</t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,14 +3314,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>75.5</t>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4553,24 +4553,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4781,32 +4781,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4814,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4838,17 +4842,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4858,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5011,32 +5015,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -5044,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5068,17 +5076,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5088,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,7 +5206,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5274,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5328,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5356,32 +5364,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5389,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5413,37 +5425,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5553,12 +5565,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5658,7 +5670,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5730,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5784,7 +5796,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5857,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5903,6 +5915,577 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,14 +4619,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5249,32 +5249,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5282,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,17 +5310,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5326,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5374,24 +5378,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>68分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5401,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5454,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5487,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5516,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5540,37 +5548,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5598,32 +5606,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -5631,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,17 +5667,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5675,13 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5725,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5742,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,37 +5786,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5824,32 +5844,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5857,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5881,37 +5905,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5963,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -5972,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5996,17 +6024,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6016,17 +6044,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6126,7 +6154,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6141,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6251,12 +6279,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6371,7 +6399,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6460,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6476,13 +6504,592 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB51" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,14 +2128,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,14 +2604,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,22 +3552,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,14 +4024,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,14 +4262,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,14 +5091,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,17 +5687,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5735,24 +5735,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5854,24 +5854,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6082,32 +6082,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6115,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6139,17 +6143,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6159,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6197,32 +6201,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6230,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6254,37 +6262,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6312,32 +6320,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6345,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6369,32 +6381,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6427,32 +6439,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -6460,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6484,17 +6500,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6504,17 +6520,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6542,32 +6558,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6575,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6599,37 +6619,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6744,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6805,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6854,12 +6874,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6920,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6969,12 +6989,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6982,22 +7002,22 @@
       <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7030,12 +7050,12 @@
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7049,47 +7069,737 @@
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V56" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W56" s="2" t="inlineStr">
+      <c r="W57" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X56" s="2" t="inlineStr">
+      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y56" s="2" t="inlineStr">
+      <c r="Y57" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z56" s="2" t="inlineStr">
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB56" s="2" t="inlineStr">
-        <is>
-          <t>77.7</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>5/15</t>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,17 +4262,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,17 +4738,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,22 +4972,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,17 +5091,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,17 +5563,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,22 +5801,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6449,24 +6449,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,17 +6515,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6568,24 +6568,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6677,32 +6677,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6710,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6734,32 +6738,32 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6792,32 +6796,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6825,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6849,17 +6857,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6869,12 +6877,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6907,32 +6915,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6940,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,37 +6976,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7022,32 +7034,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -7055,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7079,32 +7095,32 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7137,32 +7153,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7170,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7194,17 +7214,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7214,12 +7234,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7285,7 +7305,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7324,7 +7344,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7339,7 +7359,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7515,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7569,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7745,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7794,10 +7814,930 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>80.4</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
         <is>
           <t>6/15</t>
         </is>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,17 +2604,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,17 +4024,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,17 +5325,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,22 +5563,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,22 +6277,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,17 +6396,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6753,22 +6753,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7044,24 +7044,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7163,24 +7163,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7229,22 +7229,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7272,32 +7272,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -7305,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7329,17 +7333,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7349,17 +7353,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7387,32 +7391,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7420,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7444,32 +7452,32 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7502,32 +7510,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7535,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,32 +7571,32 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7617,32 +7629,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -7650,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,37 +7690,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7732,32 +7748,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -7765,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7789,17 +7809,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7809,7 +7829,7 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7847,32 +7867,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -7880,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7904,32 +7928,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7962,32 +7986,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7995,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8019,37 +8047,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8225,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8340,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8455,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8570,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8619,7 +8647,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8632,22 +8660,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8680,12 +8708,12 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8699,47 +8727,852 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr">
         <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
           <t>17:04</t>
         </is>
       </c>
-      <c r="V70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W70" s="2" t="inlineStr">
+      <c r="W71" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X70" s="2" t="inlineStr">
+      <c r="X71" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y70" s="2" t="inlineStr">
+      <c r="Y71" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z70" s="2" t="inlineStr">
+      <c r="Z71" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>76.4</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>78.3</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,14 +1771,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2009,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,22 +3195,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,14 +4619,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4972,17 +4972,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,17 +5801,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,17 +6515,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,14 +6634,14 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6991,17 +6991,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,14 +7824,14 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
           <t>79.8</t>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8105,32 +8105,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -8138,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,32 +8166,32 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8220,32 +8224,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8253,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8277,37 +8285,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8335,32 +8343,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8368,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8392,32 +8404,32 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8450,32 +8462,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8483,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8507,37 +8523,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8565,32 +8581,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -8598,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8622,17 +8642,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8642,12 +8662,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8713,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8752,7 +8772,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8767,7 +8787,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8795,32 +8815,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -8828,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8852,17 +8876,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8872,7 +8896,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8943,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9058,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9173,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9288,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9403,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9465,22 +9489,22 @@
       <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9513,12 +9537,12 @@
       <c r="M77" s="2" t="inlineStr"/>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9532,47 +9556,737 @@
       <c r="T77" s="2" t="inlineStr"/>
       <c r="U77" s="2" t="inlineStr">
         <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="V77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W77" s="2" t="inlineStr">
+      <c r="W78" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X77" s="2" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y77" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z77" s="2" t="inlineStr">
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
+      <c r="AA79" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
+      <c r="AB79" s="2" t="inlineStr">
         <is>
           <t>77.3</t>
         </is>
       </c>
-      <c r="AC77" s="2" t="inlineStr">
+      <c r="AC79" s="2" t="inlineStr">
         <is>
           <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>83.8</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,17 +4262,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,17 +5091,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,22 +6158,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,17 +7110,17 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7229,22 +7229,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8591,24 +8591,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8657,17 +8657,17 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8700,32 +8700,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8733,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8757,17 +8761,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8777,12 +8781,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8852,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8891,7 +8895,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8967,7 +8971,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9049,32 +9053,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9082,7 +9090,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,37 +9114,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9197,7 +9205,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9312,7 +9320,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9427,7 +9435,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9542,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9657,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9772,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9887,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10002,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10117,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10179,22 +10187,22 @@
       <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>18:50</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10227,12 +10235,12 @@
       <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10246,47 +10254,392 @@
       <c r="T83" s="2" t="inlineStr"/>
       <c r="U83" s="2" t="inlineStr">
         <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
           <t>18:50</t>
         </is>
       </c>
-      <c r="V83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W83" s="2" t="inlineStr">
+      <c r="W84" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X83" s="2" t="inlineStr">
+      <c r="X84" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y83" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z83" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB83" s="2" t="inlineStr">
-        <is>
-          <t>83.8</t>
-        </is>
-      </c>
-      <c r="AC83" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>84.6</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
         <is>
           <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC86"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,17 +938,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,22 +2604,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,22 +3552,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,17 +3905,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,22 +4024,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,17 +4857,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,22 +5444,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,22 +6277,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6396,17 +6396,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,22 +6634,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7363,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7467,17 +7467,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7586,22 +7586,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7705,22 +7705,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,22 +7824,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8300,17 +8300,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8710,24 +8710,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8938,32 +8938,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8971,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8995,37 +8999,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9063,24 +9067,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9090,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9139,12 +9143,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9172,32 +9176,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9205,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9229,37 +9237,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9359,7 +9367,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9374,7 +9382,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9410,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9435,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9459,32 +9471,32 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9517,32 +9529,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -9550,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9574,17 +9590,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9594,12 +9610,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9632,32 +9648,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9665,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9689,32 +9709,32 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9747,32 +9767,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9780,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9804,17 +9828,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9824,12 +9848,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9895,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9977,32 +10001,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -10010,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10034,37 +10062,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10125,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10240,7 +10268,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10279,7 +10307,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10355,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10404,7 +10432,7 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10470,7 +10498,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10524,7 +10552,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10532,22 +10560,22 @@
       <c r="A86" s="2" t="inlineStr"/>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10580,12 +10608,12 @@
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10624,22 +10652,827 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA86" s="2" t="inlineStr">
+      <c r="AA87" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB86" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr">
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
         <is>
           <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,22 +3195,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4029,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,12 +4267,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6768,7 +6768,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,12 +6877,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7234,17 +7234,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7591,17 +7591,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8538,22 +8538,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8900,12 +8900,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9019,17 +9019,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9138,17 +9138,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9605,7 +9605,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10120,32 +10120,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10153,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10177,37 +10181,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10235,32 +10239,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -10268,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10292,17 +10300,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10312,12 +10320,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10350,32 +10358,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10383,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10407,17 +10419,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10427,12 +10439,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10465,32 +10477,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -10498,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10522,17 +10538,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10542,12 +10558,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10580,32 +10596,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10613,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10637,17 +10657,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10657,17 +10677,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10695,32 +10715,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10728,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10752,17 +10776,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10772,17 +10796,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10867,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10958,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11073,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11127,7 +11151,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11227,7 +11251,7 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11242,7 +11266,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11250,22 +11274,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11298,12 +11322,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11317,7 +11341,7 @@
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
@@ -11347,17 +11371,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11365,22 +11389,22 @@
       <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11413,12 +11437,12 @@
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11432,47 +11456,507 @@
       <c r="T93" s="2" t="inlineStr"/>
       <c r="U93" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V93" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W93" s="2" t="inlineStr">
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X93" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y93" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z93" s="2" t="inlineStr">
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB93" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="AC93" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
         <is>
           <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东78路.xlsx
+++ b/data/export/2026-10-06-浦东78路.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2614,12 +2614,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5096,17 +5096,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5330,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5449,17 +5449,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6282,17 +6282,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6401,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6639,17 +6639,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7115,17 +7115,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7472,17 +7472,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7710,17 +7710,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,17 +7948,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8186,12 +8186,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8662,17 +8662,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9257,17 +9257,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,17 +9372,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9610,12 +9610,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,17 +10082,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10320,17 +10320,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10606,24 +10606,24 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10806,7 +10806,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -10834,32 +10834,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -10867,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10891,17 +10895,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10911,17 +10915,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11064,32 +11068,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11097,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11121,17 +11129,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11141,17 +11149,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -11179,32 +11187,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11212,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11236,17 +11248,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11256,17 +11268,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11393,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11409,32 +11421,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -11442,7 +11458,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11466,17 +11482,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11486,12 +11502,12 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11524,32 +11540,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11557,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11581,17 +11601,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11601,17 +11621,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -11639,32 +11659,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -11672,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11696,17 +11720,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11716,17 +11740,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11787,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11831,17 +11855,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11946,12 +11970,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
